--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/51.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/51.xlsx
@@ -426,13 +426,13 @@
         <v>-5.450189581549839</v>
       </c>
       <c r="E2">
-        <v>-15.04996429311732</v>
+        <v>-14.19592126611474</v>
       </c>
       <c r="F2">
-        <v>3.416651736010624</v>
+        <v>1.000673473906115</v>
       </c>
       <c r="G2">
-        <v>-15.22901931512387</v>
+        <v>-14.41294177924204</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.013464912697206</v>
       </c>
       <c r="E3">
-        <v>-14.776426349158</v>
+        <v>-14.762256753988</v>
       </c>
       <c r="F3">
-        <v>3.822018294774979</v>
+        <v>1.74424256241584</v>
       </c>
       <c r="G3">
-        <v>-14.20049580815423</v>
+        <v>-14.8538821760649</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-4.539094357907308</v>
       </c>
       <c r="E4">
-        <v>-14.88444403966296</v>
+        <v>-16.73571591331666</v>
       </c>
       <c r="F4">
-        <v>3.597963136400574</v>
+        <v>1.528462794395403</v>
       </c>
       <c r="G4">
-        <v>-13.97005889925599</v>
+        <v>-14.34934186175532</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.073855004936349</v>
       </c>
       <c r="E5">
-        <v>-14.91597580417837</v>
+        <v>-17.68421385117123</v>
       </c>
       <c r="F5">
-        <v>3.550438041767161</v>
+        <v>1.995918803469192</v>
       </c>
       <c r="G5">
-        <v>-13.83575029777402</v>
+        <v>-13.75683035682625</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-3.620046040556419</v>
       </c>
       <c r="E6">
-        <v>-15.36438530041789</v>
+        <v>-17.19597642603425</v>
       </c>
       <c r="F6">
-        <v>3.432604435453737</v>
+        <v>1.570996147059546</v>
       </c>
       <c r="G6">
-        <v>-13.24747156865663</v>
+        <v>-14.11666551914276</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.195291473263929</v>
       </c>
       <c r="E7">
-        <v>-15.74893425620124</v>
+        <v>-17.8815058782634</v>
       </c>
       <c r="F7">
-        <v>3.8418792316245</v>
+        <v>1.445548187579589</v>
       </c>
       <c r="G7">
-        <v>-13.37591170537954</v>
+        <v>-14.61512408929191</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.807598768302746</v>
       </c>
       <c r="E8">
-        <v>-15.79710363422083</v>
+        <v>-18.36064107064497</v>
       </c>
       <c r="F8">
-        <v>3.147773617470738</v>
+        <v>2.407759881853828</v>
       </c>
       <c r="G8">
-        <v>-12.35983551239565</v>
+        <v>-13.70220293969384</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.470026871095182</v>
       </c>
       <c r="E9">
-        <v>-15.46324641647934</v>
+        <v>-18.89957476229782</v>
       </c>
       <c r="F9">
-        <v>3.790692753070713</v>
+        <v>1.593569158785833</v>
       </c>
       <c r="G9">
-        <v>-11.90827708260643</v>
+        <v>-12.96467292611277</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.187917410590024</v>
       </c>
       <c r="E10">
-        <v>-17.16564017865687</v>
+        <v>-20.1554926866371</v>
       </c>
       <c r="F10">
-        <v>3.652030676781298</v>
+        <v>2.348238370493072</v>
       </c>
       <c r="G10">
-        <v>-11.44319345754917</v>
+        <v>-11.74648989117489</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.965084201875571</v>
       </c>
       <c r="E11">
-        <v>-18.75403866463931</v>
+        <v>-20.44014350581124</v>
       </c>
       <c r="F11">
-        <v>4.081655146569234</v>
+        <v>1.506405027193658</v>
       </c>
       <c r="G11">
-        <v>-11.48800838160807</v>
+        <v>-13.6707327437172</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.800446583665766</v>
       </c>
       <c r="E12">
-        <v>-19.94576546991986</v>
+        <v>-22.19895752565033</v>
       </c>
       <c r="F12">
-        <v>3.57213298404648</v>
+        <v>2.25113880027172</v>
       </c>
       <c r="G12">
-        <v>-9.545098659614069</v>
+        <v>-12.31503699444455</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.689625591555487</v>
       </c>
       <c r="E13">
-        <v>-20.36564105143705</v>
+        <v>-20.20568176406411</v>
       </c>
       <c r="F13">
-        <v>3.636614759415199</v>
+        <v>1.814055710388977</v>
       </c>
       <c r="G13">
-        <v>-9.263300789645838</v>
+        <v>-9.418082573047965</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.630080725682006</v>
       </c>
       <c r="E14">
-        <v>-19.74971424470579</v>
+        <v>-20.9512180253689</v>
       </c>
       <c r="F14">
-        <v>3.542841912683489</v>
+        <v>2.617418014767577</v>
       </c>
       <c r="G14">
-        <v>-8.492125130194225</v>
+        <v>-10.71616663417989</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.615623436518626</v>
       </c>
       <c r="E15">
-        <v>-20.44893780233414</v>
+        <v>-24.10838406251053</v>
       </c>
       <c r="F15">
-        <v>3.787646017763216</v>
+        <v>2.857964311396914</v>
       </c>
       <c r="G15">
-        <v>-8.22908600388134</v>
+        <v>-9.41167434734237</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.639248511062573</v>
       </c>
       <c r="E16">
-        <v>-22.44358116307068</v>
+        <v>-24.04908822385409</v>
       </c>
       <c r="F16">
-        <v>3.934991041168775</v>
+        <v>2.744857369483864</v>
       </c>
       <c r="G16">
-        <v>-7.421360817479072</v>
+        <v>-8.355990528914424</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.693348182217408</v>
       </c>
       <c r="E17">
-        <v>-23.34918086665058</v>
+        <v>-26.84994939759821</v>
       </c>
       <c r="F17">
-        <v>3.918786518035211</v>
+        <v>2.451522531743726</v>
       </c>
       <c r="G17">
-        <v>-7.318596239458823</v>
+        <v>-9.359056678415113</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.769808280919295</v>
       </c>
       <c r="E18">
-        <v>-23.03968683907036</v>
+        <v>-26.09360819731111</v>
       </c>
       <c r="F18">
-        <v>4.043977683620301</v>
+        <v>2.1921606979272</v>
       </c>
       <c r="G18">
-        <v>-6.943037463429459</v>
+        <v>-7.856831417962336</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.862650832158586</v>
       </c>
       <c r="E19">
-        <v>-24.42477495600443</v>
+        <v>-27.67587060101316</v>
       </c>
       <c r="F19">
-        <v>4.406388422345084</v>
+        <v>2.194765085041602</v>
       </c>
       <c r="G19">
-        <v>-5.79938737621436</v>
+        <v>-6.812467813914475</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.966789117329494</v>
       </c>
       <c r="E20">
-        <v>-25.35982785453023</v>
+        <v>-26.58046443787575</v>
       </c>
       <c r="F20">
-        <v>4.263140504113771</v>
+        <v>3.13650947752747</v>
       </c>
       <c r="G20">
-        <v>-6.067518958387503</v>
+        <v>-7.903759448705515</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.080576936917407</v>
       </c>
       <c r="E21">
-        <v>-26.02506068625701</v>
+        <v>-28.40967811463809</v>
       </c>
       <c r="F21">
-        <v>3.946101104775122</v>
+        <v>2.775564949105642</v>
       </c>
       <c r="G21">
-        <v>-4.495292117185533</v>
+        <v>-6.368761347317005</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.203520557776673</v>
       </c>
       <c r="E22">
-        <v>-26.41876168800986</v>
+        <v>-27.3356554057649</v>
       </c>
       <c r="F22">
-        <v>4.476047493981301</v>
+        <v>3.113179337995025</v>
       </c>
       <c r="G22">
-        <v>-3.673497052736366</v>
+        <v>-6.0901167312674</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.335639694979418</v>
       </c>
       <c r="E23">
-        <v>-26.56465553511498</v>
+        <v>-30.58370338776647</v>
       </c>
       <c r="F23">
-        <v>3.90589380777804</v>
+        <v>3.434986820104188</v>
       </c>
       <c r="G23">
-        <v>-4.2603074352059</v>
+        <v>-7.254586169277175</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.476844937300918</v>
       </c>
       <c r="E24">
-        <v>-27.54278327840174</v>
+        <v>-28.17507146172271</v>
       </c>
       <c r="F24">
-        <v>3.791572479252486</v>
+        <v>2.647386690666057</v>
       </c>
       <c r="G24">
-        <v>-3.420879086096277</v>
+        <v>-5.654186759765812</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.624761311981038</v>
       </c>
       <c r="E25">
-        <v>-27.81504419269089</v>
+        <v>-28.14078185653663</v>
       </c>
       <c r="F25">
-        <v>3.944928136532758</v>
+        <v>2.28260185096485</v>
       </c>
       <c r="G25">
-        <v>-3.530327512433115</v>
+        <v>-6.145552969514218</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.778500823779402</v>
       </c>
       <c r="E26">
-        <v>-27.43983295031136</v>
+        <v>-30.34508224264329</v>
       </c>
       <c r="F26">
-        <v>4.369131770036774</v>
+        <v>2.468494123092282</v>
       </c>
       <c r="G26">
-        <v>-3.476364542666488</v>
+        <v>-5.831100382586393</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.93472678981535</v>
       </c>
       <c r="E27">
-        <v>-28.01150750903966</v>
+        <v>-29.62886105782715</v>
       </c>
       <c r="F27">
-        <v>3.830475925957562</v>
+        <v>3.331591657621559</v>
       </c>
       <c r="G27">
-        <v>-2.106651414891885</v>
+        <v>-3.970234324464749</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.089541540669308</v>
       </c>
       <c r="E28">
-        <v>-28.34472621194607</v>
+        <v>-28.36181214437701</v>
       </c>
       <c r="F28">
-        <v>4.358275186855684</v>
+        <v>3.432205162365587</v>
       </c>
       <c r="G28">
-        <v>-1.901000853653688</v>
+        <v>-4.853568699261301</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.238221824627191</v>
       </c>
       <c r="E29">
-        <v>-27.32581956022024</v>
+        <v>-29.02132098495809</v>
       </c>
       <c r="F29">
-        <v>3.70836131690647</v>
+        <v>2.4257719026603</v>
       </c>
       <c r="G29">
-        <v>-3.177297603630899</v>
+        <v>-4.682026436133532</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-3.375965141824248</v>
       </c>
       <c r="E30">
-        <v>-26.05251229569151</v>
+        <v>-27.44082921459304</v>
       </c>
       <c r="F30">
-        <v>3.876218373940151</v>
+        <v>2.824445252810035</v>
       </c>
       <c r="G30">
-        <v>-2.320865964400233</v>
+        <v>-4.192802864063443</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.499989505828428</v>
       </c>
       <c r="E31">
-        <v>-26.63523180252452</v>
+        <v>-28.24270422102727</v>
       </c>
       <c r="F31">
-        <v>4.020067686905896</v>
+        <v>2.712877417531387</v>
       </c>
       <c r="G31">
-        <v>-3.240267526578202</v>
+        <v>-4.29180059973345</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.608038100673514</v>
       </c>
       <c r="E32">
-        <v>-26.45909680599618</v>
+        <v>-28.46263861815779</v>
       </c>
       <c r="F32">
-        <v>3.556307853183398</v>
+        <v>2.260249184967709</v>
       </c>
       <c r="G32">
-        <v>-3.740571783854535</v>
+        <v>-4.61095517715596</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.697996397310321</v>
       </c>
       <c r="E33">
-        <v>-26.39562571430467</v>
+        <v>-28.76637695527427</v>
       </c>
       <c r="F33">
-        <v>3.734312410901373</v>
+        <v>2.377231229591055</v>
       </c>
       <c r="G33">
-        <v>-3.052689933689426</v>
+        <v>-4.501565812807192</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-3.767550923402019</v>
       </c>
       <c r="E34">
-        <v>-25.37017994611177</v>
+        <v>-27.10225332693556</v>
       </c>
       <c r="F34">
-        <v>4.243261343181389</v>
+        <v>2.236001214352962</v>
       </c>
       <c r="G34">
-        <v>-3.337086531132738</v>
+        <v>-4.090372970642258</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-3.815246731676117</v>
       </c>
       <c r="E35">
-        <v>-25.4810143474495</v>
+        <v>-26.43928926068663</v>
       </c>
       <c r="F35">
-        <v>3.705352686499502</v>
+        <v>2.185573520340139</v>
       </c>
       <c r="G35">
-        <v>-3.519945727419032</v>
+        <v>-4.257994174006491</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.839758261088117</v>
       </c>
       <c r="E36">
-        <v>-24.62069938394629</v>
+        <v>-27.14656444510062</v>
       </c>
       <c r="F36">
-        <v>4.061081813753305</v>
+        <v>2.429859067425713</v>
       </c>
       <c r="G36">
-        <v>-3.537579012079488</v>
+        <v>-5.662698248491012</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.841494477228303</v>
       </c>
       <c r="E37">
-        <v>-24.39666671783882</v>
+        <v>-25.39087054385281</v>
       </c>
       <c r="F37">
-        <v>3.866612625537287</v>
+        <v>1.727391912708093</v>
       </c>
       <c r="G37">
-        <v>-5.984320304526223</v>
+        <v>-7.619897690376393</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.821134329695862</v>
       </c>
       <c r="E38">
-        <v>-23.18540407568918</v>
+        <v>-25.17043348610743</v>
       </c>
       <c r="F38">
-        <v>4.346986195890332</v>
+        <v>2.757952201387319</v>
       </c>
       <c r="G38">
-        <v>-4.954518761759178</v>
+        <v>-6.809882211325633</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.780212799251026</v>
       </c>
       <c r="E39">
-        <v>-24.78510110432076</v>
+        <v>-24.25309144942564</v>
       </c>
       <c r="F39">
-        <v>4.474795002468268</v>
+        <v>2.827438972603753</v>
       </c>
       <c r="G39">
-        <v>-5.59676538247553</v>
+        <v>-7.940673191249268</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.722517423208922</v>
       </c>
       <c r="E40">
-        <v>-23.36958164205514</v>
+        <v>-25.42329441774773</v>
       </c>
       <c r="F40">
-        <v>4.252855494440613</v>
+        <v>2.90621505587518</v>
       </c>
       <c r="G40">
-        <v>-6.241673073876592</v>
+        <v>-7.71197532977753</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.65283661075451</v>
       </c>
       <c r="E41">
-        <v>-22.4901791606096</v>
+        <v>-21.76895627625199</v>
       </c>
       <c r="F41">
-        <v>4.389218022819856</v>
+        <v>2.829309426199274</v>
       </c>
       <c r="G41">
-        <v>-6.608628486977091</v>
+        <v>-7.098337679837977</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.579143248501689</v>
       </c>
       <c r="E42">
-        <v>-21.55478209805922</v>
+        <v>-22.44729904023097</v>
       </c>
       <c r="F42">
-        <v>4.367489945844425</v>
+        <v>3.161292573484426</v>
       </c>
       <c r="G42">
-        <v>-5.649579924696352</v>
+        <v>-7.040683335816974</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.509027965060311</v>
       </c>
       <c r="E43">
-        <v>-20.4151463292889</v>
+        <v>-19.73091202062594</v>
       </c>
       <c r="F43">
-        <v>4.598047788330806</v>
+        <v>3.017189780093424</v>
       </c>
       <c r="G43">
-        <v>-5.981107988619527</v>
+        <v>-8.156269135034142</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.449981664372443</v>
       </c>
       <c r="E44">
-        <v>-21.15830061326566</v>
+        <v>-22.17429092773055</v>
       </c>
       <c r="F44">
-        <v>4.957832602388716</v>
+        <v>2.392118648554167</v>
       </c>
       <c r="G44">
-        <v>-6.600648556144522</v>
+        <v>-6.864219240350037</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.408104053583737</v>
       </c>
       <c r="E45">
-        <v>-20.17823921157763</v>
+        <v>-21.75252697255216</v>
       </c>
       <c r="F45">
-        <v>4.686732802474521</v>
+        <v>3.170861873721566</v>
       </c>
       <c r="G45">
-        <v>-7.376549174641736</v>
+        <v>-8.672602159628363</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.389158154102343</v>
       </c>
       <c r="E46">
-        <v>-18.8829190348976</v>
+        <v>-18.93728789383369</v>
       </c>
       <c r="F46">
-        <v>4.913985459023732</v>
+        <v>2.171458139796435</v>
       </c>
       <c r="G46">
-        <v>-6.763131366546665</v>
+        <v>-9.448515903011815</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.397786530487789</v>
       </c>
       <c r="E47">
-        <v>-18.67734895731941</v>
+        <v>-19.22797969733407</v>
       </c>
       <c r="F47">
-        <v>5.060029945606896</v>
+        <v>2.539927557705294</v>
       </c>
       <c r="G47">
-        <v>-7.829541498252435</v>
+        <v>-8.340841128974468</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.435987100512585</v>
       </c>
       <c r="E48">
-        <v>-18.25957005926777</v>
+        <v>-20.10394053853378</v>
       </c>
       <c r="F48">
-        <v>5.070686063876509</v>
+        <v>3.579995847433853</v>
       </c>
       <c r="G48">
-        <v>-7.357186686219452</v>
+        <v>-9.563010848107078</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.502876437730078</v>
       </c>
       <c r="E49">
-        <v>-16.86292074819212</v>
+        <v>-17.74166660090654</v>
       </c>
       <c r="F49">
-        <v>4.872744359507956</v>
+        <v>3.538484700144764</v>
       </c>
       <c r="G49">
-        <v>-9.25779489986909</v>
+        <v>-9.5624103845617</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.593809919471706</v>
       </c>
       <c r="E50">
-        <v>-17.21261403953843</v>
+        <v>-16.88031914532959</v>
       </c>
       <c r="F50">
-        <v>5.240660427991745</v>
+        <v>3.966193984497427</v>
       </c>
       <c r="G50">
-        <v>-7.973623218149211</v>
+        <v>-9.801237376987443</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.703577818623839</v>
       </c>
       <c r="E51">
-        <v>-15.90180195327817</v>
+        <v>-17.75797816428217</v>
       </c>
       <c r="F51">
-        <v>4.690584710897538</v>
+        <v>3.788823956209997</v>
       </c>
       <c r="G51">
-        <v>-7.078312384660686</v>
+        <v>-8.578500006525047</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.824947839068585</v>
       </c>
       <c r="E52">
-        <v>-14.93381799176859</v>
+        <v>-16.70169801657104</v>
       </c>
       <c r="F52">
-        <v>5.206004849328225</v>
+        <v>3.557989439011081</v>
       </c>
       <c r="G52">
-        <v>-8.357263642879488</v>
+        <v>-11.92995939467124</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.951684758849013</v>
       </c>
       <c r="E53">
-        <v>-15.50428797641086</v>
+        <v>-15.07204966085273</v>
       </c>
       <c r="F53">
-        <v>4.977814480879045</v>
+        <v>3.612136502662473</v>
       </c>
       <c r="G53">
-        <v>-8.778818582729148</v>
+        <v>-11.56481193464999</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.077125827099986</v>
       </c>
       <c r="E54">
-        <v>-13.32887699023613</v>
+        <v>-13.13758971967813</v>
       </c>
       <c r="F54">
-        <v>4.980137223076495</v>
+        <v>2.92726221484551</v>
       </c>
       <c r="G54">
-        <v>-8.633801714687928</v>
+        <v>-11.36323993181018</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.194853346284079</v>
       </c>
       <c r="E55">
-        <v>-12.72721034815503</v>
+        <v>-13.3731382951871</v>
       </c>
       <c r="F55">
-        <v>5.695197219051473</v>
+        <v>3.366901646533291</v>
       </c>
       <c r="G55">
-        <v>-7.781451915077214</v>
+        <v>-11.35636249142159</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.300473471353251</v>
       </c>
       <c r="E56">
-        <v>-12.66251656848145</v>
+        <v>-12.65662502379747</v>
       </c>
       <c r="F56">
-        <v>4.889603292889731</v>
+        <v>3.582520711277586</v>
       </c>
       <c r="G56">
-        <v>-9.952774032267278</v>
+        <v>-13.33383660132278</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.389950604115185</v>
       </c>
       <c r="E57">
-        <v>-13.40107897981443</v>
+        <v>-12.22007560098404</v>
       </c>
       <c r="F57">
-        <v>5.40854233604751</v>
+        <v>3.189906040311926</v>
       </c>
       <c r="G57">
-        <v>-8.687987807520599</v>
+        <v>-10.54151705423532</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.462919532894812</v>
       </c>
       <c r="E58">
-        <v>-11.97316508418982</v>
+        <v>-10.32690175733737</v>
       </c>
       <c r="F58">
-        <v>5.399907434240728</v>
+        <v>3.603470122894385</v>
       </c>
       <c r="G58">
-        <v>-9.330250834344749</v>
+        <v>-11.22378145309066</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.518640263545986</v>
       </c>
       <c r="E59">
-        <v>-10.45043852826662</v>
+        <v>-12.28787591382688</v>
       </c>
       <c r="F59">
-        <v>5.052258202633831</v>
+        <v>3.34733063827475</v>
       </c>
       <c r="G59">
-        <v>-9.633655548281924</v>
+        <v>-11.74769738070876</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.557155307000075</v>
       </c>
       <c r="E60">
-        <v>-11.08335616947466</v>
+        <v>-11.73436506434334</v>
       </c>
       <c r="F60">
-        <v>5.088065211987242</v>
+        <v>3.891614410488582</v>
       </c>
       <c r="G60">
-        <v>-9.085051709650564</v>
+        <v>-12.18199002265219</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.579042454813441</v>
       </c>
       <c r="E61">
-        <v>-10.3923382067482</v>
+        <v>-10.0808471221306</v>
       </c>
       <c r="F61">
-        <v>5.68043405519878</v>
+        <v>2.878925320157353</v>
       </c>
       <c r="G61">
-        <v>-9.246051407907837</v>
+        <v>-12.17581804489887</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.585887425089137</v>
       </c>
       <c r="E62">
-        <v>-10.36778482067862</v>
+        <v>-10.59136916785932</v>
       </c>
       <c r="F62">
-        <v>5.070442523860086</v>
+        <v>3.66199427990217</v>
       </c>
       <c r="G62">
-        <v>-8.983107437020175</v>
+        <v>-11.87575033328765</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.581844229009436</v>
       </c>
       <c r="E63">
-        <v>-9.720520973814278</v>
+        <v>-11.92102876293951</v>
       </c>
       <c r="F63">
-        <v>4.900617265877353</v>
+        <v>3.212606620618244</v>
       </c>
       <c r="G63">
-        <v>-9.503125273425653</v>
+        <v>-12.20065689210387</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.570607462860416</v>
       </c>
       <c r="E64">
-        <v>-10.34960752601183</v>
+        <v>-11.46652846915967</v>
       </c>
       <c r="F64">
-        <v>4.792294974082873</v>
+        <v>2.883897181308956</v>
       </c>
       <c r="G64">
-        <v>-9.372903433395971</v>
+        <v>-13.54148542649068</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.555644891887494</v>
       </c>
       <c r="E65">
-        <v>-9.773390907853829</v>
+        <v>-9.162776001133565</v>
       </c>
       <c r="F65">
-        <v>4.687022731065501</v>
+        <v>3.282051973464538</v>
       </c>
       <c r="G65">
-        <v>-9.16691490633715</v>
+        <v>-13.45884129907294</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.539003099090045</v>
       </c>
       <c r="E66">
-        <v>-10.76395384076565</v>
+        <v>-11.47797192297706</v>
       </c>
       <c r="F66">
-        <v>4.611833478648196</v>
+        <v>3.528633754990672</v>
       </c>
       <c r="G66">
-        <v>-9.359043553528876</v>
+        <v>-11.13298349009771</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.524397031892359</v>
       </c>
       <c r="E67">
-        <v>-9.6236523863162</v>
+        <v>-9.756513285227241</v>
       </c>
       <c r="F67">
-        <v>4.627221231522599</v>
+        <v>3.343059575945916</v>
       </c>
       <c r="G67">
-        <v>-8.74713510735115</v>
+        <v>-12.4413377747107</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.514368977279037</v>
       </c>
       <c r="E68">
-        <v>-10.92274931031862</v>
+        <v>-10.44384054163744</v>
       </c>
       <c r="F68">
-        <v>4.2760796029455</v>
+        <v>3.465081407847894</v>
       </c>
       <c r="G68">
-        <v>-8.853692777494118</v>
+        <v>-12.42847866741923</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.511803208200875</v>
       </c>
       <c r="E69">
-        <v>-10.88291232447314</v>
+        <v>-10.25822292053704</v>
       </c>
       <c r="F69">
-        <v>4.667012688083476</v>
+        <v>2.060064261672375</v>
       </c>
       <c r="G69">
-        <v>-7.958523036532648</v>
+        <v>-10.22773055528407</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.518054131029053</v>
       </c>
       <c r="E70">
-        <v>-9.412068495255818</v>
+        <v>-10.27245138586914</v>
       </c>
       <c r="F70">
-        <v>4.009559018033981</v>
+        <v>2.393140853929222</v>
       </c>
       <c r="G70">
-        <v>-7.61412602165333</v>
+        <v>-10.53926285502399</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.532917328508921</v>
       </c>
       <c r="E71">
-        <v>-9.317880764370283</v>
+        <v>-10.51449379310511</v>
       </c>
       <c r="F71">
-        <v>4.369420041892949</v>
+        <v>2.710125581019287</v>
       </c>
       <c r="G71">
-        <v>-8.346714515565873</v>
+        <v>-11.23753633386786</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.557191837201302</v>
       </c>
       <c r="E72">
-        <v>-10.47181292558282</v>
+        <v>-11.30414644819263</v>
       </c>
       <c r="F72">
-        <v>4.016908293631618</v>
+        <v>2.354058479865141</v>
       </c>
       <c r="G72">
-        <v>-6.966721320645531</v>
+        <v>-10.23181567612558</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.590515892423281</v>
       </c>
       <c r="E73">
-        <v>-9.978797960367748</v>
+        <v>-13.03113435270581</v>
       </c>
       <c r="F73">
-        <v>3.435220419711777</v>
+        <v>2.375430358857368</v>
       </c>
       <c r="G73">
-        <v>-7.351506891700053</v>
+        <v>-9.142541992593594</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.635514356640456</v>
       </c>
       <c r="E74">
-        <v>-9.979604028741115</v>
+        <v>-11.11362448974192</v>
       </c>
       <c r="F74">
-        <v>3.411799159765025</v>
+        <v>1.488783995801306</v>
       </c>
       <c r="G74">
-        <v>-6.135742117051478</v>
+        <v>-9.482506077146102</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.693450224642123</v>
       </c>
       <c r="E75">
-        <v>-10.21684172505495</v>
+        <v>-8.500699515790137</v>
       </c>
       <c r="F75">
-        <v>3.588965409671366</v>
+        <v>3.344373366646756</v>
       </c>
       <c r="G75">
-        <v>-6.993771711181593</v>
+        <v>-7.803921720316291</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.765206680409941</v>
       </c>
       <c r="E76">
-        <v>-8.74112525780537</v>
+        <v>-10.71997782967716</v>
       </c>
       <c r="F76">
-        <v>3.66766362640693</v>
+        <v>2.56756023752788</v>
       </c>
       <c r="G76">
-        <v>-6.735257389399182</v>
+        <v>-9.193656862046625</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.851379372250418</v>
       </c>
       <c r="E77">
-        <v>-10.18840290828678</v>
+        <v>-12.78956290676664</v>
       </c>
       <c r="F77">
-        <v>3.485836981492439</v>
+        <v>2.00826313450571</v>
       </c>
       <c r="G77">
-        <v>-6.014103952621303</v>
+        <v>-6.929456487394917</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.951275135022733</v>
       </c>
       <c r="E78">
-        <v>-11.12897148815392</v>
+        <v>-11.67484280198652</v>
       </c>
       <c r="F78">
-        <v>3.111901995459908</v>
+        <v>1.904738746708245</v>
       </c>
       <c r="G78">
-        <v>-6.444419754034681</v>
+        <v>-7.000074937797287</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.068137505554055</v>
       </c>
       <c r="E79">
-        <v>-12.45654345671657</v>
+        <v>-12.81127693963342</v>
       </c>
       <c r="F79">
-        <v>2.707774674330141</v>
+        <v>1.524145343492012</v>
       </c>
       <c r="G79">
-        <v>-5.241425493695465</v>
+        <v>-8.054193613541377</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.203802776013362</v>
       </c>
       <c r="E80">
-        <v>-13.3015250072298</v>
+        <v>-14.30663339865426</v>
       </c>
       <c r="F80">
-        <v>2.498389902659316</v>
+        <v>1.984850158232985</v>
       </c>
       <c r="G80">
-        <v>-4.149999328820487</v>
+        <v>-8.085352093469863</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.359557350445407</v>
       </c>
       <c r="E81">
-        <v>-12.95131094137261</v>
+        <v>-12.25037562056936</v>
       </c>
       <c r="F81">
-        <v>3.125086291042865</v>
+        <v>1.849349131952653</v>
       </c>
       <c r="G81">
-        <v>-5.218932719905471</v>
+        <v>-5.906604571890775</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.536199148982393</v>
       </c>
       <c r="E82">
-        <v>-14.47526471375189</v>
+        <v>-16.5131685866837</v>
       </c>
       <c r="F82">
-        <v>2.980347311486513</v>
+        <v>1.113619712543022</v>
       </c>
       <c r="G82">
-        <v>-4.116521025249473</v>
+        <v>-6.095514340732686</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.733633031320431</v>
       </c>
       <c r="E83">
-        <v>-15.03239381396756</v>
+        <v>-14.31876518052081</v>
       </c>
       <c r="F83">
-        <v>2.419882210426396</v>
+        <v>1.042921868183695</v>
       </c>
       <c r="G83">
-        <v>-3.133316109848102</v>
+        <v>-6.080381346900527</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.952121385353707</v>
       </c>
       <c r="E84">
-        <v>-14.78327793033161</v>
+        <v>-13.12246914496652</v>
       </c>
       <c r="F84">
-        <v>2.590786002767573</v>
+        <v>1.657827274955796</v>
       </c>
       <c r="G84">
-        <v>-3.780412376029313</v>
+        <v>-7.195120590955359</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.192934226951699</v>
       </c>
       <c r="E85">
-        <v>-15.43587179110297</v>
+        <v>-17.3389358219824</v>
       </c>
       <c r="F85">
-        <v>2.584791936240916</v>
+        <v>0.5151010697331004</v>
       </c>
       <c r="G85">
-        <v>-3.904416301203848</v>
+        <v>-3.810402741082638</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.455880967885681</v>
       </c>
       <c r="E86">
-        <v>-17.7260569510021</v>
+        <v>-16.7824995782899</v>
       </c>
       <c r="F86">
-        <v>2.197011617437994</v>
+        <v>0.9414766825672564</v>
       </c>
       <c r="G86">
-        <v>-3.04209158805242</v>
+        <v>-6.007721976688183</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.739126713511318</v>
       </c>
       <c r="E87">
-        <v>-17.28534133210162</v>
+        <v>-18.7151843576535</v>
       </c>
       <c r="F87">
-        <v>2.542079656217767</v>
+        <v>0.9267831015763988</v>
       </c>
       <c r="G87">
-        <v>-2.86109284439033</v>
+        <v>-5.10607182314681</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.040793224924811</v>
       </c>
       <c r="E88">
-        <v>-18.98935628797389</v>
+        <v>-20.24058271324122</v>
       </c>
       <c r="F88">
-        <v>1.959855000220913</v>
+        <v>0.6567088205068703</v>
       </c>
       <c r="G88">
-        <v>-2.752067695634661</v>
+        <v>-4.885271861968657</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.356595559561309</v>
       </c>
       <c r="E89">
-        <v>-20.88949492464436</v>
+        <v>-20.86899905128564</v>
       </c>
       <c r="F89">
-        <v>2.131171319528684</v>
+        <v>0.5748901437649604</v>
       </c>
       <c r="G89">
-        <v>-2.615194819503984</v>
+        <v>-5.139671531915524</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.688006771513344</v>
       </c>
       <c r="E90">
-        <v>-23.234891239645</v>
+        <v>-23.94829797786537</v>
       </c>
       <c r="F90">
-        <v>1.600767671516161</v>
+        <v>-0.2642882820084816</v>
       </c>
       <c r="G90">
-        <v>-2.528737912634175</v>
+        <v>-3.162213828122131</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.033857708077182</v>
       </c>
       <c r="E91">
-        <v>-23.90277775714027</v>
+        <v>-22.36417437134618</v>
       </c>
       <c r="F91">
-        <v>1.057060443014677</v>
+        <v>0.1409821861371485</v>
       </c>
       <c r="G91">
-        <v>-2.725568550320585</v>
+        <v>-3.338651673816593</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.392811545583211</v>
       </c>
       <c r="E92">
-        <v>-26.39189425172235</v>
+        <v>-24.22064493316068</v>
       </c>
       <c r="F92">
-        <v>1.199248050970406</v>
+        <v>0.2001806342108124</v>
       </c>
       <c r="G92">
-        <v>-2.066938790357926</v>
+        <v>-3.674028610628997</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.763353082985503</v>
       </c>
       <c r="E93">
-        <v>-25.719234722623</v>
+        <v>-26.73752097340978</v>
       </c>
       <c r="F93">
-        <v>1.185818558636221</v>
+        <v>-0.630571638341353</v>
       </c>
       <c r="G93">
-        <v>-1.791782112826011</v>
+        <v>-5.716228097011793</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.139217070060948</v>
       </c>
       <c r="E94">
-        <v>-29.16861865900558</v>
+        <v>-29.374908763951</v>
       </c>
       <c r="F94">
-        <v>1.090972147750483</v>
+        <v>-0.1150206178610247</v>
       </c>
       <c r="G94">
-        <v>-2.705123258783685</v>
+        <v>-5.482063720422021</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.523311441330018</v>
       </c>
       <c r="E95">
-        <v>-29.28848736598862</v>
+        <v>-31.28170425741274</v>
       </c>
       <c r="F95">
-        <v>0.4877293256423963</v>
+        <v>-1.675269673484158</v>
       </c>
       <c r="G95">
-        <v>-2.930894270624398</v>
+        <v>-3.845764465828773</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.91444065391973</v>
       </c>
       <c r="E96">
-        <v>-33.4305104587924</v>
+        <v>-32.21902139294238</v>
       </c>
       <c r="F96">
-        <v>0.2373436810026066</v>
+        <v>-1.235747041600171</v>
       </c>
       <c r="G96">
-        <v>-1.365367683846813</v>
+        <v>-6.011633192787041</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.30800052074495</v>
       </c>
       <c r="E97">
-        <v>-34.61514114530294</v>
+        <v>-34.91545142759561</v>
       </c>
       <c r="F97">
-        <v>-0.08891213405958989</v>
+        <v>-1.399120145882498</v>
       </c>
       <c r="G97">
-        <v>-2.466079705735019</v>
+        <v>-5.004032395091198</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.69878724058908</v>
       </c>
       <c r="E98">
-        <v>-36.37592731557237</v>
+        <v>-36.08635404515189</v>
       </c>
       <c r="F98">
-        <v>-0.3562188396363651</v>
+        <v>-2.042428614161788</v>
       </c>
       <c r="G98">
-        <v>-3.44780807143464</v>
+        <v>-6.767784138717957</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.07441260259762</v>
       </c>
       <c r="E99">
-        <v>-39.05950327675482</v>
+        <v>-37.19340744343702</v>
       </c>
       <c r="F99">
-        <v>-0.8899972564478937</v>
+        <v>-1.183767815441905</v>
       </c>
       <c r="G99">
-        <v>-2.943599160502568</v>
+        <v>-3.796549423658662</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.43197797122549</v>
       </c>
       <c r="E100">
-        <v>-41.31138207502308</v>
+        <v>-42.11402465780159</v>
       </c>
       <c r="F100">
-        <v>-0.8568625603359136</v>
+        <v>-2.117855608023697</v>
       </c>
       <c r="G100">
-        <v>-2.966420056448506</v>
+        <v>-6.437496376544252</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.75249003387774</v>
       </c>
       <c r="E101">
-        <v>-44.10930426913621</v>
+        <v>-44.04915481312933</v>
       </c>
       <c r="F101">
-        <v>-1.110878939302174</v>
+        <v>-2.183220423043801</v>
       </c>
       <c r="G101">
-        <v>-4.115618689320626</v>
+        <v>-8.12644611228035</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.03959456761262</v>
       </c>
       <c r="E102">
-        <v>-45.81337356669658</v>
+        <v>-44.786349625312</v>
       </c>
       <c r="F102">
-        <v>-1.096839768559527</v>
+        <v>-2.894254553441173</v>
       </c>
       <c r="G102">
-        <v>-4.475890254104536</v>
+        <v>-7.911181571872979</v>
       </c>
     </row>
   </sheetData>
